--- a/РЭ/07. РЭ ЮНИТ-М3-ВВ/_hardware/description.xlsx
+++ b/РЭ/07. РЭ ЮНИТ-М3-ВВ/_hardware/description.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Инфо" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Номер</t>
   </si>
@@ -46,19 +46,22 @@
     <t>code_bu</t>
   </si>
   <si>
-    <t>МИКРОПРОЦЕССОРНОЕ УСТРОЙСТВО ЗАЩИТЫ И АВТОМАТИКИ ОТХОДЯЩЕЙ ЛИНИИ</t>
-  </si>
-  <si>
-    <t>ЮТКБ.656122.609 БУ2</t>
-  </si>
-  <si>
-    <t>ЮНИТ-М319-ОЛ-Р02с-x-K002-K002-K002-K002-K002-B021-B021-B021-B021-М046.3001-х-С01.00</t>
-  </si>
-  <si>
     <t>ЮНИТ-ИЧМ-СНГР-К-С</t>
   </si>
   <si>
     <t>1.0</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>МИКРОПРОЦЕССОРНОЕ УСТРОЙСТВО ЗАЩИТЫ И АВТОМАТИКИ ВВОДНОГО ВЫКЛЮЧАТЕЛЯ</t>
+  </si>
+  <si>
+    <t>ЮТКБ.656122.609 БУ3</t>
+  </si>
+  <si>
+    <t>ЮНИТ-М319-ВВ-Р02с-x-К002-K001-K001-К001-B021-B021-B021-В001-х-М037.ab00-х-С01.a0</t>
   </si>
 </sst>
 </file>
@@ -110,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -118,6 +121,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -423,7 +427,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2"/>
     </row>
@@ -432,7 +436,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2"/>
       <c r="E3" s="3"/>
@@ -442,7 +446,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -450,7 +454,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -464,12 +468,12 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" style="5" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -477,20 +481,26 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
+      <c r="A2" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="B2" s="4">
         <v>45873</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="4"/>
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4">
+        <v>45923</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>